--- a/光伏配储项目/电价数据/2026/四黎站.xlsx
+++ b/光伏配储项目/电价数据/2026/四黎站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.7235199999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.97951</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.8098200000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5916699999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.69609</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.02074</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44206</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45963</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43177</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42645</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41282</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40467</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41662</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.4205</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42437</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.4174</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41514</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44732</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.5017900000000001</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40075</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.12432</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.13674</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11563</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.42088</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.19273</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28723</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05149</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.81635</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.27873</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14812</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21928</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22987</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23534</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21905</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.72351</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.23094</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.43403</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.15053</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29111</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.43354</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.6130399999999999</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.70596</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.24717</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73127</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.73633</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39454</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43143</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43648</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65825</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.41061</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.01854</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.74729</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.00725</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.59212</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.93425</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.8277899999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.17126</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>-0.01342</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.28542</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.59405</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.22788</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8693099999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7963899999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75702</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5183099999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47942</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46988</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41568</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42532</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70833</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76473</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.86998</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9143</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49382</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51442</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50238</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50263</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48489</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4670299999999999</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37349</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.86926</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.71205</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.80724</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45526</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43615</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42678</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50881</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50754</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7794</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.99391</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52599</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.8979600000000001</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8525499999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.5013299999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.72468</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.36949</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.08914</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.03789</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37468</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47337</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.54638</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.4992799999999999</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5259199999999999</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.8988700000000001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6274299999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.8657899999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.07485</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.36496</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.18426</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.99638</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.41102</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.31307</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.46837</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.24771</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.29808</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.8540800000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.19057</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9015</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.24179</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.18259</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.9838300000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45036</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.78862</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80798</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44896</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42811</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44366</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33459</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50757</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48638</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48759</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44857</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41428</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38266</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44298</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39541</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39496</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47192</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44388</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43776</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.42495</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.70335</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.6696</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.23996</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.39567</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.40942</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.55733</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.49971</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.59537</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.72805</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8159</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.53342</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.53399</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.80336</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.0655</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6747300000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.60192</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49411</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.44848</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42598</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.68157</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51286</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50602</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57038</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.59585</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.54457</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.56459</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26528</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61627</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.27047</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.43773</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.52152</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.55992</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.8142200000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.83365</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.44822</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.6216499999999999</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.67591</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.5569400000000001</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.71966</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61014</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.7892100000000001</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56279</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.05746</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.7662599999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.56053</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48363</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6173099999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.49059</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.4567</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34194</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52338</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49288</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44585</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38903</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.45518</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38697</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44855</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41544</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.47885</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.59468</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.4999</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.6366799999999999</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.81776</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.59904</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.6329600000000001</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.9365599999999999</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.51825</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.10318</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.9438099999999999</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.8547899999999999</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.6392</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.01867</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.70469</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.4411600000000001</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6029</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48117</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40504</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39811</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.64224</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.65307</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.5938600000000001</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.0419</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.01231</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49449</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46158</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47407</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5204500000000001</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.82138</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.70353</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.03913</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.75249</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.68653</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5001100000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.62912</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.59315</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.53101</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41546</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.45293</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.45892</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31782</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.62126</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.4193</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.20407</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.21236</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.12487</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.22603</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29241</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.07203</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.27533</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18736</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.05276</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38271</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22391</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.02865</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21441</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06327000000000001</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.00161</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00312</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.02385</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27381</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.27238</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40052</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46078</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48507</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34372</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.58445</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.40208</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.38549</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.28521</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.2646</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.28299</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29167</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10276</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04357</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04474</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01692</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21938</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05583</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.21246</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.07277</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07352</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.07177</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3312</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3128</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39479</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42754</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45531</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78522</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8628899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.1871</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.85753</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33086</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307999999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77299</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49316</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.3999</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20701</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44961</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.40886</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42609</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44922</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5572999999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.41018</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58386</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.70652</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87634</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46646</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5505599999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43314</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.81372</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.56677</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85319</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.62488</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30273</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.63282</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5940800000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.28619</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.42186</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39115</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34708</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9135</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.43589</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.46018</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28811</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.1907</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27322</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19773</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25368</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27436</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30154</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41089</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42018</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.43979</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.53086</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8656200000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.4458</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13835</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.68609</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.77637</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6376900000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5023</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.4397799999999999</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.48972</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43006</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41548</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40488</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40425</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.40366</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.46108</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40449</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42503</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42564</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.39853</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41585</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40452</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48627</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28746</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.52342</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.22392</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24832</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27552</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.00718</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25983</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25291</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28174</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5414500000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43176</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7836000000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.43294</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43452</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44065</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3068</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.29823</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.28535</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.28064</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.28073</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.24072</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.28769</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.24497</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.29534</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.23811</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.27377</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26378</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.25352</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.17379</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22968</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.07815999999999999</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>-0.0308</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.2253</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.02875</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.18905</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>-0.03166</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.21608</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.00632</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.19682</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.25167</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.26905</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.03035</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.03092</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.11387</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.21138</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.13992</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.26553</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.25859</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.24595</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.41585</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.41988</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.40764</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39436</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33405</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.48944</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.43425</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.41817</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29449</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.28945</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28986</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.17327</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.5977899999999999</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25277</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2805299999999999</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30133</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.2391</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.43528</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.42892</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.42288</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.47428</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.46237</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.60685</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.6890499999999999</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.63642</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.76764</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.5861499999999999</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.79369</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.89093</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39212</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.57329</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.42369</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.34828</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.45931</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.47198</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37347</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.2674</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.03921</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.02567</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.03362</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.40126</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.5440900000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.22942</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.03954999999999999</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.02427</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.20055</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>-0.00429</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.38805</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.25604</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.01447</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.06781000000000001</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.00461</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.59715</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.22529</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.9788600000000001</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.77703</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.43108</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.6582100000000001</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.53632</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.43483</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.55955</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.26657</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.51201</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.8100499999999999</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.83256</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.56803</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.63349</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.10998</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.64071</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.69667</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.6246499999999999</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.11008</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.74537</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.34731</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.7249800000000001</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.70692</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.98189</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.65438</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.64864</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.60375</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.51463</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50293</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.23997</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.79123</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30864</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.58027</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39586</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41387</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.36297</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.28503</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.90223</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.43961</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.7138300000000001</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.23932</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.92088</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.47792</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.7110599999999999</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.70352</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34261</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.27181</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.66299</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.12185</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.5049399999999999</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.40591</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.46321</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5397799999999999</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.41393</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.45904</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.40632</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.55872</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65023</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.42631</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.5518099999999999</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.55887</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.78288</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.64234</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33336</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40407</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.07847</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.42854</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.68698</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.47805</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.6845399999999999</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.4172</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.55361</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.75752</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29743</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27701</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.5745399999999999</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.6095700000000001</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.49362</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.7189</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.63301</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.0182</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.60145</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.57888</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.77373</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.60809</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.7625299999999999</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.05836</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.06338</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.69859</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.09408</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.90965</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.86751</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.15237</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.75188</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.00534</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.7606000000000001</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.4962</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.60864</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.75437</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.66564</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.10628</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.04007</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.65258</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.40431</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.39548</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3495</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.45194</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52325</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47107</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.61049</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.38795</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39352</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39235</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.38871</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.41098</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.41347</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.49836</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.45569</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.41806</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.45321</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.56425</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.07026</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.77966</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.1175</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.15411</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.4462</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.23372</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.4274</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.5953200000000001</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.59742</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.62034</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.5112</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.54257</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.5336900000000001</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.61309</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.8621</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.86142</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.20039</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.58654</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.59172</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.58143</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.57712</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.3392</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.31544</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.33415</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.34921</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>1.33739</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>1.35634</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>1.3515</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>1.35391</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>1.35913</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.36987</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41043</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.45448</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.41735</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.46747</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.46768</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.49965</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.61345</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.71802</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.80528</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.5766699999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.7017</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.80467</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.8651599999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7215900000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76455</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61726</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66553</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.9115700000000001</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.67563</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.44446</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44103</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.43423</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.39526</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.50059</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40331</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42745</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41737</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.41556</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.4091</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.49383</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39495</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>1.35137</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.5922200000000001</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.5644600000000001</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.55816</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.57994</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.56899</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.8055</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.5809299999999999</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.65773</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.61753</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>1.66795</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.39495</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.15908</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.22157</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.58902</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.45445</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41042</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40108</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39132</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.36853</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.32851</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.45546</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.9605199999999999</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.83539</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.28992</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.27181</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.25949</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.25205</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.25113</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.24533</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.28626</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.27877</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.2406</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30197</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.18408</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28216</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24737</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27148</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26366</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25975</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.26985</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25806</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03338</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28196</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.19789</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.25121</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25791</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24112</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27627</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27434</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.47459</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.46316</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.321</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.65708</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.26593</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.28669</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.23415</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.24485</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.23318</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.23626</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.23625</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.23308</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.23308</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.23498</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28015</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.2294</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.23308</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.23339</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.27922</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.23332</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.23312</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23998</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15978</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.2659</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.20677</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01216</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00036</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14545</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02109</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01539</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04283</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04072</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04858</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04823</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02921</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04939</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00012</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27399</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03843</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01915</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03619</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20114</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26446</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27911</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.2373</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.32853</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.71946</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.61736</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.41391</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.41057</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.2571</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.28268</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.25748</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.23263</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26671</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.25943</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28606</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.25244</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.27799</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43553</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.25737</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6516900000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.8192200000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8752000000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.84838</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.12419</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.21366</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29905</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.26581</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.25635</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.27074</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.01729</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27298</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00637</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06406999999999999</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.28814</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25764</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.4709</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39727</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.48891</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.7918999999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.75419</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.77611</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.34084</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.99799</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.75775</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.83651</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.7811399999999999</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83963</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83782</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.84214</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.93937</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.74012</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.7770900000000001</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7434299999999999</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36187</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.46212</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.60123</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.6299199999999999</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5635</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49277</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.45661</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.38841</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.4715299999999999</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.27322</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.45739</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.46742</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.44696</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.42113</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.40065</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.27682</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.38697</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.4084</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.38151</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.45992</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46542</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.73509</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.60566</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.47146</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.42436</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.40732</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.46736</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3366</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.41866</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.42162</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40639</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.5463300000000001</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.75759</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.5407000000000001</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5361</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.56416</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39466</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.46135</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.43685</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.45453</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.45841</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.4044</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.45101</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.43807</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.01128</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.6260800000000001</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.4938</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.0427</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.84327</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.13783</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.77311</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.12565</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.00498</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.5681</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.45378</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.45204</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.6366499999999999</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.7442300000000001</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.87363</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.47796</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.43337</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.41828</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23413</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35142</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.45247</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37641</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39133</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43508</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.95575</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.40382</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.5709099999999999</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.4138</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.5984400000000001</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.44679</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.38976</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.50112</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.45658</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3732200000000001</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37405</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41771</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51474</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.82555</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.7071000000000001</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.70388</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.09403</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.62524</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47556</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.24846</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.96258</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.18375</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.07536</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.99851</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.7938099999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.67701</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.67006</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.42572</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35582</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.22383</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.43638</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.38323</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.97858</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.51502</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.80777</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.00348</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.5508200000000001</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.39681</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1.0571</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.51924</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.48873</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>1.09831</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.6083099999999999</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.64435</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.9802000000000001</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.44801</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.51505</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.97084</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>1.13412</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.9779600000000001</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.5355800000000001</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.43636</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.41384</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.44825</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.97961</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.84627</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.42643</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.58153</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.08155</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.5141699999999999</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.59946</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.43272</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.62625</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.9871799999999999</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.46004</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.65891</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.4812</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.6074700000000001</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.64676</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.6106900000000001</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.91769</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40486</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.49004</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36231</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.18477</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.85551</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.56425</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.6175</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.93161</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.4428</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38259</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.7722599999999999</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.42788</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.45917</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.65912</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.46986</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.9702799999999999</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.7095900000000001</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.45703</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42644</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40395</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.4478</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.4753</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.6080399999999999</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.54957</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.51976</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.45085</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.44343</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.02903</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.25892</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.9560700000000001</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.53242</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.6598099999999999</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.78495</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.71736</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.47198</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3581</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17539</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14508</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19766</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14146</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12235</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22765</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26957</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.15347</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14416</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19858</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22575</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26145</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15263</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15136</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19627</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14225</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27895</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.41986</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.4247</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.29845</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.41361</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.42429</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.43637</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.9498</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.68001</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.5057699999999999</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.26661</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.42648</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.53474</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.45656</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39455</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.45633</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49939</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39635</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.5133799999999999</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.45689</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.45831</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.48134</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38279</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38378</v>
       </c>
     </row>
   </sheetData>
